--- a/Inputs.xlsx
+++ b/Inputs.xlsx
@@ -229,7 +229,7 @@
     <t xml:space="preserve">Display on plot?</t>
   </si>
   <si>
-    <t xml:space="preserve">Colour on graph</t>
+    <t xml:space="preserve">Colour on plot</t>
   </si>
   <si>
     <t xml:space="preserve">brown</t>
@@ -257,8 +257,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -402,7 +403,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -424,6 +425,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -788,7 +793,7 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>40</v>
@@ -805,14 +810,14 @@
       <c r="F4" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="G4" s="3" t="b">
+      <c r="G4" s="6" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" s="3" t="b">
+        <v>30</v>
+      </c>
+      <c r="I4" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -823,6 +828,7 @@
         <v>2</v>
       </c>
       <c r="L4" s="3" t="b">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
@@ -849,13 +855,13 @@
       <c r="K5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="7"/>
+      <c r="N5" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -998,7 +1004,7 @@
       <c r="M12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="9" t="s">
         <v>38</v>
       </c>
       <c r="B13" s="3" t="n">
@@ -1121,7 +1127,7 @@
         <v>3000</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>2500</v>
@@ -1271,13 +1277,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>0</v>
